--- a/test_data/mycobot_320.xlsx
+++ b/test_data/mycobot_320.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" firstSheet="35" activeTab="42"/>
+    <workbookView windowWidth="23040" windowHeight="9060" firstSheet="42" activeTab="50"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -51,6 +51,13 @@
     <sheet name="stop" sheetId="42" r:id="rId42"/>
     <sheet name="is_in_position" sheetId="43" r:id="rId43"/>
     <sheet name="is_moving" sheetId="44" r:id="rId44"/>
+    <sheet name="jog_angle" sheetId="45" r:id="rId45"/>
+    <sheet name="jog_coord" sheetId="46" r:id="rId46"/>
+    <sheet name="jog_increment_angle" sheetId="47" r:id="rId47"/>
+    <sheet name="jog_increment_coord" sheetId="48" r:id="rId48"/>
+    <sheet name="set_encoder" sheetId="49" r:id="rId49"/>
+    <sheet name="set_encoders" sheetId="50" r:id="rId50"/>
+    <sheet name="set_joint_min" sheetId="51" r:id="rId51"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="368">
   <si>
     <t>ID</t>
   </si>
@@ -807,6 +814,12 @@
     <t>刷新模式暂停单坐标运动</t>
   </si>
   <si>
+    <t>下电时暂停</t>
+  </si>
+  <si>
+    <t>resume</t>
+  </si>
+  <si>
     <t>expect_data_1</t>
   </si>
   <si>
@@ -816,40 +829,172 @@
     <t>插补模式多角度运动-是否暂停移动命令</t>
   </si>
   <si>
+    <t>is_paused</t>
+  </si>
+  <si>
     <t>插补模式单角度运动-是否暂停移动命令</t>
   </si>
   <si>
-    <t>插补模式多坐标运动-是否移动命令</t>
-  </si>
-  <si>
-    <t>插补模式单坐标运动-是否移动命令</t>
-  </si>
-  <si>
-    <t>刷新模式多角度运动-是否移动命令</t>
-  </si>
-  <si>
-    <t>刷新模式单角度运动-是否移动命令</t>
-  </si>
-  <si>
-    <t>刷新模式多坐标运动-是否移动命令</t>
-  </si>
-  <si>
-    <t>刷新模式单坐标运动-是否移动命令</t>
+    <t>插补模式多坐标运动-是否暂停移动命令</t>
+  </si>
+  <si>
+    <t>插补模式单坐标运动-是否暂停移动命令</t>
+  </si>
+  <si>
+    <t>刷新模式多角度运动-是否暂停移动命令</t>
+  </si>
+  <si>
+    <t>刷新模式单角度运动-是否暂停移动命令</t>
+  </si>
+  <si>
+    <t>刷新模式多坐标运动-是否暂停移动命令</t>
+  </si>
+  <si>
+    <t>刷新模式单坐标运动-是否暂停移动命令</t>
+  </si>
+  <si>
+    <t>下电时-是否暂停移动命令</t>
+  </si>
+  <si>
+    <t>插补模式恢复多角度运动</t>
+  </si>
+  <si>
+    <t>插补模式恢复单角度运动</t>
+  </si>
+  <si>
+    <t>插补模式恢复多坐标运动</t>
+  </si>
+  <si>
+    <t>插补模式恢复单坐标运动</t>
+  </si>
+  <si>
+    <t>刷新模式恢复多角度运动</t>
+  </si>
+  <si>
+    <t>刷新模式恢复单角度运动</t>
+  </si>
+  <si>
+    <t>刷新模式恢复多坐标运动</t>
+  </si>
+  <si>
+    <t>刷新模式恢复单坐标运动</t>
+  </si>
+  <si>
+    <t>下电时恢复</t>
+  </si>
+  <si>
+    <t>插补模式停止多角度运动</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>插补模式停止单角度运动</t>
+  </si>
+  <si>
+    <t>插补模式停止多坐标运动</t>
+  </si>
+  <si>
+    <t>插补模式停止单坐标运动</t>
+  </si>
+  <si>
+    <t>刷新模式停止多角度运动</t>
+  </si>
+  <si>
+    <t>刷新模式停止单角度运动</t>
+  </si>
+  <si>
+    <t>刷新模式停止多坐标运动</t>
+  </si>
+  <si>
+    <t>刷新模式停止单坐标运动</t>
+  </si>
+  <si>
+    <t>下电时停止</t>
   </si>
   <si>
     <t>data</t>
   </si>
   <si>
-    <t>角度运动，是否到达点位</t>
+    <t>目标角度与运动角度一致，是否到达点位</t>
   </si>
   <si>
     <t>is_in_position</t>
   </si>
   <si>
+    <t>[0, 10, -100, 0, 90, 0]</t>
+  </si>
+  <si>
+    <t>目标角度与运动角度不一致，是否到达点位</t>
+  </si>
+  <si>
     <t>坐标运动，是否到达点位</t>
   </si>
   <si>
-    <t>[260, -89.4, 235.9, 178.24, 0.18, -90.0],</t>
+    <t>[-1.9, -154.2, 523.8, -89.99, 0.43, -177.29]</t>
+  </si>
+  <si>
+    <t>logic_1</t>
+  </si>
+  <si>
+    <t>目标坐标与运动坐标不一致，是否到达点位</t>
+  </si>
+  <si>
+    <t>[190.2, -89.4, 235.9, 178.24, 0.18, -90.0]</t>
+  </si>
+  <si>
+    <t>是否到达点位-1关节超限</t>
+  </si>
+  <si>
+    <t>exception_1</t>
+  </si>
+  <si>
+    <t>是否到达点位-2关节超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-3关节超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-4关节超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-5关节超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-6关节超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-1坐标超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-2坐标超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-3坐标超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-4坐标超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-5坐标超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-6坐标超限</t>
+  </si>
+  <si>
+    <t>是否到达点位-模式超限</t>
+  </si>
+  <si>
+    <t>exception_2</t>
+  </si>
+  <si>
+    <t>下电时角度是否到达点位</t>
+  </si>
+  <si>
+    <t>logic_2</t>
+  </si>
+  <si>
+    <t>下电时坐标是否到达点位</t>
   </si>
   <si>
     <t>角度运动，是否运动</t>
@@ -862,6 +1007,180 @@
   </si>
   <si>
     <t>停止运动，是否运动</t>
+  </si>
+  <si>
+    <t>下电时是否运动</t>
+  </si>
+  <si>
+    <t>direction</t>
+  </si>
+  <si>
+    <t>点动控制角度-负方向</t>
+  </si>
+  <si>
+    <t>jog_angle</t>
+  </si>
+  <si>
+    <t>点动控制角度-正方向</t>
+  </si>
+  <si>
+    <t>设置方向超限</t>
+  </si>
+  <si>
+    <t>点动控制坐标-负方向</t>
+  </si>
+  <si>
+    <t>jog_coord</t>
+  </si>
+  <si>
+    <t>点动控制坐标-正方向</t>
+  </si>
+  <si>
+    <t>increment</t>
+  </si>
+  <si>
+    <t>关节步进模式-正增量</t>
+  </si>
+  <si>
+    <t>jog_increment_angle</t>
+  </si>
+  <si>
+    <t>关节步进模式-负增量</t>
+  </si>
+  <si>
+    <t>设置增量超限</t>
+  </si>
+  <si>
+    <t>坐标步进模式-正增量</t>
+  </si>
+  <si>
+    <t>jog_increment_coord</t>
+  </si>
+  <si>
+    <t>坐标步进模式-负增量</t>
+  </si>
+  <si>
+    <t>encoder</t>
+  </si>
+  <si>
+    <t>发送单关节电位值</t>
+  </si>
+  <si>
+    <t>set_encoder</t>
+  </si>
+  <si>
+    <t>设置1关节电位值超限</t>
+  </si>
+  <si>
+    <t>设置2关节电位值超限</t>
+  </si>
+  <si>
+    <t>设置3关节电位值超限</t>
+  </si>
+  <si>
+    <t>设置4关节电位值超限</t>
+  </si>
+  <si>
+    <t>设置5关节电位值超限</t>
+  </si>
+  <si>
+    <t>设置6关节电位值超限</t>
+  </si>
+  <si>
+    <t>encoders</t>
+  </si>
+  <si>
+    <t>速度30发送多关节电位值</t>
+  </si>
+  <si>
+    <t>set_encoders</t>
+  </si>
+  <si>
+    <t>[3000, 3000, 3000, 3000, 3000, 3000]</t>
+  </si>
+  <si>
+    <t>速度50发送多关节电位值</t>
+  </si>
+  <si>
+    <t>速度70发送多关节电位值</t>
+  </si>
+  <si>
+    <t>[1000, 1000, 1000, 1000, 1000, 1000]</t>
+  </si>
+  <si>
+    <t>[-1, 2048, 2048, 2048, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2049, 2048, 2048, 2048, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, -1, 2048, 2048, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2049, 2048, 2048, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, -1, 2048, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2049, 2048, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2048, -1, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2048, 2049, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2048, 2048, -1, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2048, 2048, 2049, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2048, 2048, 2048, -1]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2048, 2048, 2048, 2049]</t>
+  </si>
+  <si>
+    <t>设置不同的数组长度</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2048, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>[2048, 2048, 2048, 2048, 2048, 2048, 2048]</t>
+  </si>
+  <si>
+    <t>设置1关节软件限位最小值</t>
+  </si>
+  <si>
+    <t>set_joint_min</t>
+  </si>
+  <si>
+    <t>设置2关节软件限位最小值</t>
+  </si>
+  <si>
+    <t>设置3关节软件限位最小值</t>
+  </si>
+  <si>
+    <t>设置4关节软件限位最小值</t>
+  </si>
+  <si>
+    <t>设置5关节软件限位最小值</t>
+  </si>
+  <si>
+    <t>设置6关节软件限位最小值</t>
+  </si>
+  <si>
+    <t>运动到全关节45位置</t>
+  </si>
+  <si>
+    <t>设置超限关节</t>
+  </si>
+  <si>
+    <t>设置超限角度</t>
   </si>
 </sst>
 </file>
@@ -876,7 +1195,7 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -885,15 +1204,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Courier New"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1361,137 +1693,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1504,16 +1836,31 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1836,11 +2183,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="8" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="13" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="8" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="13" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1875,7 +2222,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="9">
+      <c r="E2" s="14">
         <v>1.5</v>
       </c>
       <c r="F2" t="s">
@@ -1883,7 +2230,7 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="8">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1892,7 +2239,7 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="13">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
@@ -2193,7 +2540,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="12">
         <v>-168</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2213,7 +2560,7 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="12">
         <v>-135</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -2233,7 +2580,7 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="12">
         <v>-145</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -2253,7 +2600,7 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="12">
         <v>-148</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -2273,7 +2620,7 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="12">
         <v>-168</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -2293,7 +2640,7 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="12">
         <v>-180</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -2386,7 +2733,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="12">
         <v>168</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2406,7 +2753,7 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="12">
         <v>135</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -2426,7 +2773,7 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="12">
         <v>145</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -2446,7 +2793,7 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="12">
         <v>148</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -2466,7 +2813,7 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="12">
         <v>168</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -2486,7 +2833,7 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="12">
         <v>180</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -2896,7 +3243,7 @@
       <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3461,7 +3808,7 @@
       <c r="D2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3532,7 +3879,7 @@
       <c r="D2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3565,11 +3912,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="8" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="13" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="8" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="13" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3604,7 +3951,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="9">
+      <c r="E2" s="14">
         <v>5.2</v>
       </c>
       <c r="F2" t="s">
@@ -3612,7 +3959,7 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="8">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -3621,7 +3968,7 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="13">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
@@ -3679,7 +4026,7 @@
       <c r="D2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3750,7 +4097,7 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3821,7 +4168,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3892,7 +4239,7 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4155,7 +4502,7 @@
       <c r="C2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>126</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4208,7 +4555,7 @@
       <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>129</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4225,7 +4572,7 @@
       <c r="C3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="12" t="s">
         <v>129</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4278,7 +4625,7 @@
       <c r="C2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>133</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4295,7 +4642,7 @@
       <c r="C3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="12" t="s">
         <v>133</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4348,7 +4695,7 @@
       <c r="C2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>137</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4365,7 +4712,7 @@
       <c r="C3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="12" t="s">
         <v>137</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4418,7 +4765,7 @@
       <c r="C2" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>141</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4435,7 +4782,7 @@
       <c r="C3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="12" t="s">
         <v>141</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4454,11 +4801,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="8" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="13" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="8" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="13" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4493,7 +4840,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="9">
+      <c r="E2" s="14">
         <v>2.4</v>
       </c>
       <c r="F2" t="s">
@@ -4501,7 +4848,7 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="8">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4510,7 +4857,7 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="13">
         <v>2.4</v>
       </c>
       <c r="F3" t="s">
@@ -4563,7 +4910,7 @@
       <c r="C2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>145</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4580,7 +4927,7 @@
       <c r="C3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="12" t="s">
         <v>145</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4638,7 +4985,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="12" t="s">
         <v>149</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -4658,7 +5005,7 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="12" t="s">
         <v>149</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -4678,7 +5025,7 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="12" t="s">
         <v>149</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -4698,7 +5045,7 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="12" t="s">
         <v>149</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -4718,7 +5065,7 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="12" t="s">
         <v>149</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -4738,7 +5085,7 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="12" t="s">
         <v>149</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -6538,7 +6885,7 @@
       <c r="C20" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="3">
@@ -6559,7 +6906,7 @@
       <c r="C21" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E21" s="3">
@@ -7571,7 +7918,7 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
@@ -7699,7 +8046,7 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:5">
       <c r="A8" s="2">
@@ -7733,6 +8080,23 @@
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:5">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -7836,7 +8200,7 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
@@ -7857,10 +8221,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -7871,10 +8235,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -7891,10 +8255,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -7911,10 +8275,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -7931,10 +8295,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -7951,10 +8315,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -7971,10 +8335,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -7985,17 +8349,17 @@
       <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="J7" s="11"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -8012,10 +8376,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -8025,6 +8389,23 @@
       </c>
       <c r="F9" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:6">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -8036,9 +8417,215 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="16383" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:10">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:6">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -8047,9 +8634,216 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3"/>
+    <col min="5" max="16383" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:6">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:10">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:6">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:6">
+      <c r="A10" s="10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-1</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -8058,8 +8852,8 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
@@ -8079,7 +8873,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>75</v>
@@ -8096,13 +8890,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>141</v>
+        <v>281</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -8119,54 +8913,634 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>259</v>
+        <v>141</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="43.2" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" ht="43.2" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" ht="28.8" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" ht="28.8" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" ht="28.8" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:7">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" ht="28.8" spans="1:7">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:7">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" ht="28.8" spans="1:7">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="15" ht="28.8" spans="1:7">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="16" ht="28.8" spans="1:7">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="17" ht="28.8" spans="1:7">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="18" ht="43.2" spans="1:7">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="19" ht="43.2" spans="1:7">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="20" ht="28.8" spans="1:7">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" ht="28.8" spans="5:7">
-      <c r="E4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" ht="28.8" spans="5:7">
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" ht="28.8" spans="5:7">
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="28.8" spans="5:7">
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>23</v>
+      <c r="B20" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="21" ht="43.2" spans="1:7">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" ht="43.2" spans="1:7">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23" ht="28.8" spans="1:7">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="24" ht="43.2" spans="1:7">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" ht="28.8" spans="1:7">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" ht="43.2" spans="1:7">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="27" ht="43.2" spans="1:7">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" ht="43.2" spans="1:7">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" ht="43.2" spans="1:7">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" ht="28.8" spans="1:7">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" ht="28.8" spans="1:7">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="32" ht="28.8" spans="1:7">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="33" ht="43.2" spans="1:7">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -8178,8 +9552,8 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
@@ -8210,10 +9584,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>260</v>
+        <v>306</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -8227,10 +9601,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -8244,15 +9618,3399 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" ht="28.8" spans="1:5">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="6">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="8" width="9" style="3"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:9">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>50</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>-168</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>-135</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>-145</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-148</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>50</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-168</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>-180</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>50</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6">
+        <v>168</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>50</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6">
+        <v>135</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>50</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>145</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6">
+        <v>148</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>50</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6">
+        <v>168</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>50</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <v>180</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>50</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>50</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>50</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>50</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:9">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:9">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>101</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="7" width="9" style="3"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>50</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>50</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>50</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>50</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>50</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>50</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>50</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>50</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>50</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>50</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>50</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>101</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="8" width="9" style="3"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:9">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>45</v>
+      </c>
+      <c r="F2" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>45</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>45</v>
+      </c>
+      <c r="F3" s="3">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>45</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>45</v>
+      </c>
+      <c r="F4" s="3">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>45</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>45</v>
+      </c>
+      <c r="F5" s="3">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>45</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>45</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>45</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>45</v>
+      </c>
+      <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>45</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-45</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6">
+        <v>-45</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-45</v>
+      </c>
+      <c r="F9" s="3">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6">
+        <v>-45</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-45</v>
+      </c>
+      <c r="F10" s="3">
+        <v>50</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>-45</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-45</v>
+      </c>
+      <c r="F11" s="3">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6">
+        <v>-45</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-45</v>
+      </c>
+      <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6">
+        <v>-45</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-45</v>
+      </c>
+      <c r="F13" s="3">
+        <v>100</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <v>-45</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>50</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>50</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>101</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>169</v>
+      </c>
+      <c r="F18" s="3">
+        <v>50</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>-169</v>
+      </c>
+      <c r="F19" s="3">
+        <v>50</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="28.8" spans="1:9">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>136</v>
+      </c>
+      <c r="F20" s="3">
+        <v>50</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" ht="28.8" spans="1:9">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-136</v>
+      </c>
+      <c r="F21" s="3">
+        <v>50</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:9">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>146</v>
+      </c>
+      <c r="F22" s="3">
+        <v>50</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" ht="28.8" spans="1:9">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-146</v>
+      </c>
+      <c r="F23" s="3">
+        <v>50</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" ht="28.8" spans="1:9">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
+        <v>149</v>
+      </c>
+      <c r="F24" s="3">
+        <v>50</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="28.8" spans="1:9">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D25" s="1">
+        <v>4</v>
+      </c>
+      <c r="E25" s="3">
+        <v>-149</v>
+      </c>
+      <c r="F25" s="3">
+        <v>50</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" ht="28.8" spans="1:9">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D26" s="1">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>169</v>
+      </c>
+      <c r="F26" s="3">
+        <v>50</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" ht="28.8" spans="1:9">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D27" s="1">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-169</v>
+      </c>
+      <c r="F27" s="3">
+        <v>50</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" ht="28.8" spans="1:9">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D28" s="1">
+        <v>6</v>
+      </c>
+      <c r="E28" s="3">
+        <v>181</v>
+      </c>
+      <c r="F28" s="3">
+        <v>50</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" ht="28.8" spans="1:9">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D29" s="1">
+        <v>6</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-181</v>
+      </c>
+      <c r="F29" s="3">
+        <v>50</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="8" width="9" style="3"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:9">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>30</v>
+      </c>
+      <c r="F2" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>30</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3">
+        <v>10</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>30</v>
+      </c>
+      <c r="F4" s="3">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>30</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>30</v>
+      </c>
+      <c r="F7" s="3">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>30</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-30</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6">
+        <v>-30</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-30</v>
+      </c>
+      <c r="F9" s="3">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6">
+        <v>-30</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-30</v>
+      </c>
+      <c r="F10" s="3">
+        <v>50</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>-30</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-30</v>
+      </c>
+      <c r="F11" s="3">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6">
+        <v>-30</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-30</v>
+      </c>
+      <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6">
+        <v>-30</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="31.2" spans="1:9">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-30</v>
+      </c>
+      <c r="F13" s="3">
+        <v>100</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <v>-30</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>50</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>50</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>101</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>351</v>
+      </c>
+      <c r="F18" s="3">
+        <v>50</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>-351</v>
+      </c>
+      <c r="F19" s="3">
+        <v>50</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4">
+        <v>351</v>
+      </c>
+      <c r="F20" s="3">
+        <v>50</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4">
+        <v>-351</v>
+      </c>
+      <c r="F21" s="3">
+        <v>50</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="4">
+        <v>525</v>
+      </c>
+      <c r="F22" s="3">
+        <v>50</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="4">
+        <v>-42</v>
+      </c>
+      <c r="F23" s="3">
+        <v>50</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4</v>
+      </c>
+      <c r="E24" s="4">
+        <v>181</v>
+      </c>
+      <c r="F24" s="3">
+        <v>50</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D25" s="1">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4">
+        <v>-181</v>
+      </c>
+      <c r="F25" s="3">
+        <v>50</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D26" s="1">
+        <v>5</v>
+      </c>
+      <c r="E26" s="4">
+        <v>181</v>
+      </c>
+      <c r="F26" s="3">
+        <v>50</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D27" s="1">
+        <v>5</v>
+      </c>
+      <c r="E27" s="4">
+        <v>-181</v>
+      </c>
+      <c r="F27" s="3">
+        <v>50</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D28" s="1">
+        <v>6</v>
+      </c>
+      <c r="E28" s="4">
+        <v>181</v>
+      </c>
+      <c r="F28" s="3">
+        <v>50</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:9">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D29" s="1">
+        <v>6</v>
+      </c>
+      <c r="E29" s="4">
+        <v>-181</v>
+      </c>
+      <c r="F29" s="3">
+        <v>50</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.26851851851852" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="3"/>
+    <col min="6" max="6" width="9.17592592592593" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F2" s="3">
+        <v>30</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F3" s="3">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F4" s="3">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F5" s="3">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F6" s="3">
+        <v>70</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F7" s="3">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>30</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>50</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="3">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>70</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="3">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2048</v>
+      </c>
+      <c r="F14" s="3">
+        <v>50</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" s="1">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2048</v>
+      </c>
+      <c r="F15" s="3">
+        <v>50</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>50</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4097</v>
+      </c>
+      <c r="F17" s="3">
+        <v>50</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F18" s="3">
+        <v>50</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>4097</v>
+      </c>
+      <c r="F19" s="3">
+        <v>50</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F20" s="3">
+        <v>50</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4097</v>
+      </c>
+      <c r="F21" s="3">
+        <v>50</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D22" s="1">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F22" s="3">
+        <v>50</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4097</v>
+      </c>
+      <c r="F23" s="3">
+        <v>50</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F24" s="3">
+        <v>50</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D25" s="1">
+        <v>5</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4097</v>
+      </c>
+      <c r="F25" s="3">
+        <v>50</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D26" s="1">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F26" s="3">
+        <v>50</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D27" s="1">
+        <v>6</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4097</v>
+      </c>
+      <c r="F27" s="3">
+        <v>50</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2048</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2048</v>
+      </c>
+      <c r="F29" s="3">
+        <v>101</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -8353,6 +13111,1044 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6666666666667" style="3" customWidth="1"/>
+    <col min="5" max="6" width="9" style="3"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E2" s="3">
+        <v>30</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E3" s="3">
+        <v>50</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E4" s="3">
+        <v>70</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E5" s="3">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E6" s="3">
+        <v>50</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E7" s="3">
+        <v>70</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="3">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E9" s="3">
+        <v>50</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E10" s="3">
+        <v>50</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E11" s="3">
+        <v>50</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E12" s="3">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E13" s="3">
+        <v>50</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E14" s="3">
+        <v>50</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E15" s="3">
+        <v>50</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E16" s="3">
+        <v>50</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E17" s="3">
+        <v>50</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E18" s="3">
+        <v>50</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="43.2" spans="1:7">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="E19" s="3">
+        <v>50</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="43.2" spans="1:7">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E20" s="3">
+        <v>50</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" ht="57.6" spans="1:7">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E21" s="3">
+        <v>50</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" ht="43.2" spans="1:7">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" ht="43.2" spans="1:7">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="3">
+        <v>256</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-30</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>-30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>-30</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>-30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-30</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-30</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>-30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-30</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>-30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-30</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-168</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>-168</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-135</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>-135</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-145</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-145</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-148</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>-148</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-168</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>-168</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-180</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>-180</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D15" s="1">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-30</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" ht="28.8" spans="1:8">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-169</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" ht="28.8" spans="1:8">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>-136</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="28.8" spans="1:8">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>-146</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="28.8" spans="1:8">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-149</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" ht="28.8" spans="1:8">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>-169</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:8">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D22" s="1">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1">
+        <v>-181</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>

--- a/test_data/mycobot_320.xlsx
+++ b/test_data/mycobot_320.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" firstSheet="42" activeTab="50"/>
+    <workbookView windowWidth="28800" windowHeight="12300" firstSheet="43" activeTab="51"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -58,6 +58,7 @@
     <sheet name="set_encoder" sheetId="49" r:id="rId49"/>
     <sheet name="set_encoders" sheetId="50" r:id="rId50"/>
     <sheet name="set_joint_min" sheetId="51" r:id="rId51"/>
+    <sheet name="set_joint_max" sheetId="52" r:id="rId52"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="378">
   <si>
     <t>ID</t>
   </si>
@@ -1177,10 +1178,40 @@
     <t>运动到全关节45位置</t>
   </si>
   <si>
+    <t>[-45,-45,-45,-45,-45,-45]</t>
+  </si>
+  <si>
+    <t>[-30,-30,-30,-30,-30,-30]</t>
+  </si>
+  <si>
     <t>设置超限关节</t>
   </si>
   <si>
     <t>设置超限角度</t>
+  </si>
+  <si>
+    <t>设置1关节软件限位最大值</t>
+  </si>
+  <si>
+    <t>set_joint_max</t>
+  </si>
+  <si>
+    <t>设置2关节软件限位最大值</t>
+  </si>
+  <si>
+    <t>设置3关节软件限位最大值</t>
+  </si>
+  <si>
+    <t>设置4关节软件限位最大值</t>
+  </si>
+  <si>
+    <t>设置5关节软件限位最大值</t>
+  </si>
+  <si>
+    <t>设置6关节软件限位最大值</t>
+  </si>
+  <si>
+    <t>[30,30,30,30,30,30]</t>
   </si>
 </sst>
 </file>
@@ -1823,7 +1854,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1841,9 +1872,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2183,11 +2211,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="13" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="12" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="13" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="12" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2222,7 +2250,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <v>1.5</v>
       </c>
       <c r="F2" t="s">
@@ -2230,7 +2258,7 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2239,7 +2267,7 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
@@ -2540,7 +2568,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <v>-168</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2560,7 +2588,7 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>-135</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -2580,7 +2608,7 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>-145</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -2600,7 +2628,7 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>-148</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -2620,7 +2648,7 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>-168</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -2640,7 +2668,7 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>-180</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -2733,7 +2761,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="11">
         <v>168</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2753,7 +2781,7 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>135</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -2773,7 +2801,7 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>145</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -2793,7 +2821,7 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>148</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -2813,7 +2841,7 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="11">
         <v>168</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -2833,7 +2861,7 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <v>180</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -3243,7 +3271,7 @@
       <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3808,7 +3836,7 @@
       <c r="D2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3879,7 +3907,7 @@
       <c r="D2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3912,11 +3940,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="13" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="12" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="13" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="12" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3951,7 +3979,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <v>5.2</v>
       </c>
       <c r="F2" t="s">
@@ -3959,7 +3987,7 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -3968,7 +3996,7 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>-1</v>
       </c>
       <c r="F3" t="s">
@@ -4026,7 +4054,7 @@
       <c r="D2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4097,7 +4125,7 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4168,7 +4196,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4239,7 +4267,7 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4502,7 +4530,7 @@
       <c r="C2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>126</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4555,7 +4583,7 @@
       <c r="C2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>129</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4572,7 +4600,7 @@
       <c r="C3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>129</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4625,7 +4653,7 @@
       <c r="C2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>133</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4642,7 +4670,7 @@
       <c r="C3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>133</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4695,7 +4723,7 @@
       <c r="C2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>137</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4712,7 +4740,7 @@
       <c r="C3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>137</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4765,7 +4793,7 @@
       <c r="C2" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>141</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4782,7 +4810,7 @@
       <c r="C3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>141</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4801,11 +4829,11 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2222222222222" style="13" customWidth="1"/>
+    <col min="1" max="1" width="13.2222222222222" style="12" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="14.7777777777778" customWidth="1"/>
-    <col min="5" max="5" width="14.7777777777778" style="13" customWidth="1"/>
+    <col min="5" max="5" width="14.7777777777778" style="12" customWidth="1"/>
     <col min="6" max="6" width="14.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4840,7 +4868,7 @@
         <v>15</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="14">
+      <c r="E2" s="13">
         <v>2.4</v>
       </c>
       <c r="F2" t="s">
@@ -4848,7 +4876,7 @@
       </c>
     </row>
     <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="13">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4857,7 +4885,7 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>2.4</v>
       </c>
       <c r="F3" t="s">
@@ -4910,7 +4938,7 @@
       <c r="C2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>145</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -4927,7 +4955,7 @@
       <c r="C3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>145</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -4985,7 +5013,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>149</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -5005,7 +5033,7 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>149</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -5025,7 +5053,7 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>149</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -5045,7 +5073,7 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>149</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -5065,7 +5093,7 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>149</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -5085,7 +5113,7 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>149</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -6885,7 +6913,7 @@
       <c r="C20" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="3">
@@ -6906,7 +6934,7 @@
       <c r="C21" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E21" s="3">
@@ -8046,7 +8074,7 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="11"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:5">
       <c r="A8" s="2">
@@ -8349,7 +8377,7 @@
       <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="11"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="43.2" spans="1:6">
       <c r="A8" s="2">
@@ -8566,7 +8594,7 @@
       <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="11"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A8" s="2">
@@ -8783,7 +8811,7 @@
       <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="11"/>
+      <c r="J7" s="10"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="28.8" spans="1:6">
       <c r="A8" s="2">
@@ -8826,20 +8854,20 @@
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:6">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>277</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>-1</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="8"/>
+      <c r="F10" s="8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -9631,19 +9659,19 @@
       </c>
     </row>
     <row r="5" ht="28.8" spans="1:5">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>310</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>-1</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>302</v>
       </c>
     </row>
@@ -9700,7 +9728,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>312</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -9729,7 +9757,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>312</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -9758,7 +9786,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>312</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -9787,7 +9815,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>312</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -9816,7 +9844,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>312</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -9845,7 +9873,7 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>312</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -9892,7 +9920,7 @@
       <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>168</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -9921,7 +9949,7 @@
       <c r="G9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>135</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -9950,7 +9978,7 @@
       <c r="G10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <v>145</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -9979,7 +10007,7 @@
       <c r="G11" s="3">
         <v>1</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <v>148</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -10008,7 +10036,7 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>168</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -10037,7 +10065,7 @@
       <c r="G13" s="3">
         <v>1</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>180</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -10048,7 +10076,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>180</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -10244,10 +10272,10 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D2" s="1">
@@ -10270,10 +10298,10 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D3" s="1">
@@ -10296,10 +10324,10 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D4" s="1">
@@ -10322,10 +10350,10 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D5" s="1">
@@ -10348,10 +10376,10 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D6" s="1">
@@ -10374,10 +10402,10 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D7" s="1">
@@ -10400,10 +10428,10 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D8" s="1">
@@ -10426,10 +10454,10 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D9" s="1">
@@ -10452,10 +10480,10 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D10" s="1">
@@ -10478,10 +10506,10 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D11" s="1">
@@ -10504,10 +10532,10 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D12" s="1">
@@ -10530,10 +10558,10 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D13" s="1">
@@ -10556,10 +10584,10 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D14" s="1">
@@ -10583,7 +10611,7 @@
       <c r="B15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D15" s="1">
@@ -10607,7 +10635,7 @@
       <c r="B16" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D16" s="1">
@@ -10631,7 +10659,7 @@
       <c r="B17" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D17" s="1">
@@ -10655,7 +10683,7 @@
       <c r="B18" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D18" s="1">
@@ -10679,7 +10707,7 @@
       <c r="B19" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>317</v>
       </c>
       <c r="D19" s="1">
@@ -10932,7 +10960,7 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>-45</v>
       </c>
       <c r="F8" s="3">
@@ -10941,7 +10969,7 @@
       <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>-45</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -10961,7 +10989,7 @@
       <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>-45</v>
       </c>
       <c r="F9" s="3">
@@ -10970,7 +10998,7 @@
       <c r="G9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>-45</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -10990,7 +11018,7 @@
       <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>-45</v>
       </c>
       <c r="F10" s="3">
@@ -10999,7 +11027,7 @@
       <c r="G10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <v>-45</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -11019,7 +11047,7 @@
       <c r="D11" s="1">
         <v>4</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <v>-45</v>
       </c>
       <c r="F11" s="3">
@@ -11028,7 +11056,7 @@
       <c r="G11" s="3">
         <v>1</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <v>-45</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -11048,7 +11076,7 @@
       <c r="D12" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>-45</v>
       </c>
       <c r="F12" s="3">
@@ -11057,7 +11085,7 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>-45</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -11077,7 +11105,7 @@
       <c r="D13" s="1">
         <v>6</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>-45</v>
       </c>
       <c r="F13" s="3">
@@ -11086,7 +11114,7 @@
       <c r="G13" s="3">
         <v>1</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>-45</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -11097,7 +11125,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>180</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -11709,7 +11737,7 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <v>-30</v>
       </c>
       <c r="F8" s="3">
@@ -11718,7 +11746,7 @@
       <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <v>-30</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -11738,7 +11766,7 @@
       <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <v>-30</v>
       </c>
       <c r="F9" s="3">
@@ -11747,7 +11775,7 @@
       <c r="G9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <v>-30</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -11767,7 +11795,7 @@
       <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <v>-30</v>
       </c>
       <c r="F10" s="3">
@@ -11776,7 +11804,7 @@
       <c r="G10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <v>-30</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -11796,7 +11824,7 @@
       <c r="D11" s="1">
         <v>4</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <v>-30</v>
       </c>
       <c r="F11" s="3">
@@ -11805,7 +11833,7 @@
       <c r="G11" s="3">
         <v>1</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <v>-30</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -11825,7 +11853,7 @@
       <c r="D12" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <v>-30</v>
       </c>
       <c r="F12" s="3">
@@ -11834,7 +11862,7 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>-30</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -11854,7 +11882,7 @@
       <c r="D13" s="1">
         <v>6</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <v>-30</v>
       </c>
       <c r="F13" s="3">
@@ -11863,7 +11891,7 @@
       <c r="G13" s="3">
         <v>1</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>-30</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -11874,7 +11902,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>180</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -13594,7 +13622,6 @@
       <c r="E22" s="3">
         <v>-1</v>
       </c>
-      <c r="F22" s="3"/>
       <c r="G22" s="1" t="s">
         <v>23</v>
       </c>
@@ -13615,7 +13642,6 @@
       <c r="E23" s="3">
         <v>256</v>
       </c>
-      <c r="F23" s="3"/>
       <c r="G23" s="1" t="s">
         <v>23</v>
       </c>
@@ -13635,7 +13661,11 @@
     <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="14.787037037037" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="15.0185185185185" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
@@ -13820,324 +13850,812 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:2">
-      <c r="A8" s="2"/>
+    <row r="8" s="1" customFormat="1" ht="57.6" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
       <c r="B8" s="1" t="s">
         <v>365</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E9" s="1">
-        <v>-168</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>-168</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F9" s="1"/>
       <c r="H9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A10" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>359</v>
       </c>
       <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-30</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:8">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-169</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="28.8" spans="1:8">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D12" s="1">
         <v>2</v>
       </c>
+      <c r="E12" s="1">
+        <v>-136</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:8">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-146</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" ht="28.8" spans="1:8">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-149</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="28.8" spans="1:8">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-169</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" ht="28.8" spans="1:8">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D16" s="1">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-181</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" ht="28.8" spans="1:8">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>169</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" ht="28.8" spans="1:8">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>136</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" ht="28.8" spans="1:8">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>146</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="28.8" spans="1:8">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1">
+        <v>149</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" ht="28.8" spans="1:8">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>169</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:8">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D22" s="1">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1">
+        <v>181</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="14.787037037037" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="15.0185185185185" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:8">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>30</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>30</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D9" s="1">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="28.8" spans="1:8">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
       <c r="E10" s="1">
-        <v>-135</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>-135</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A11" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D11" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>-145</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1">
-        <v>-145</v>
+        <v>-169</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A12" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D12" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
-        <v>-148</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1">
-        <v>-148</v>
+        <v>-136</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A13" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D13" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" s="1">
-        <v>-168</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1">
-        <v>-168</v>
+        <v>-146</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A14" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D14" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1">
-        <v>-180</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1">
-        <v>-180</v>
+        <v>-149</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A15" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D15" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1">
-        <v>-30</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>-169</v>
+      </c>
       <c r="H15" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A16" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E16" s="1">
-        <v>-30</v>
+        <v>-181</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="28.8" spans="1:8">
+    <row r="17" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A17" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="1">
-        <v>-169</v>
+        <v>169</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:8">
+    <row r="18" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A18" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
       </c>
       <c r="E18" s="1">
-        <v>-136</v>
+        <v>136</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:8">
+    <row r="19" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A19" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
       <c r="E19" s="1">
-        <v>-146</v>
+        <v>146</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:8">
+    <row r="20" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A20" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
       </c>
       <c r="E20" s="1">
-        <v>-149</v>
+        <v>149</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:8">
+    <row r="21" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A21" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D21" s="1">
         <v>5</v>
       </c>
       <c r="E21" s="1">
-        <v>-169</v>
+        <v>169</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="1:8">
+    <row r="22" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A22" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="D22" s="1">
         <v>6</v>
       </c>
       <c r="E22" s="1">
-        <v>-181</v>
+        <v>181</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>23</v>

--- a/test_data/mycobot_320.xlsx
+++ b/test_data/mycobot_320.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300" firstSheet="43" activeTab="51"/>
+    <workbookView windowWidth="23040" windowHeight="9060" firstSheet="47" activeTab="52"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -59,6 +59,7 @@
     <sheet name="set_encoders" sheetId="50" r:id="rId50"/>
     <sheet name="set_joint_min" sheetId="51" r:id="rId51"/>
     <sheet name="set_joint_max" sheetId="52" r:id="rId52"/>
+    <sheet name="set_servo_calibration" sheetId="53" r:id="rId53"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="380">
   <si>
     <t>ID</t>
   </si>
@@ -1212,6 +1213,12 @@
   </si>
   <si>
     <t>[30,30,30,30,30,30]</t>
+  </si>
+  <si>
+    <t>设置指定关节零位</t>
+  </si>
+  <si>
+    <t>set_servo_calibration</t>
   </si>
 </sst>
 </file>
@@ -1867,6 +1874,9 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1881,9 +1891,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -3271,7 +3278,7 @@
       <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3836,7 +3843,7 @@
       <c r="D2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3907,7 +3914,7 @@
       <c r="D2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4054,7 +4061,7 @@
       <c r="D2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4125,7 +4132,7 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4196,7 +4203,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4267,7 +4274,7 @@
       <c r="D2" s="1">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6913,7 +6920,7 @@
       <c r="C20" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="3">
@@ -6934,7 +6941,7 @@
       <c r="C21" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>33</v>
       </c>
       <c r="E21" s="3">
@@ -8854,20 +8861,20 @@
       </c>
     </row>
     <row r="10" ht="28.8" spans="1:6">
-      <c r="A10" s="9">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>277</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>-1</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="9"/>
+      <c r="F10" s="9" t="s">
         <v>23</v>
       </c>
     </row>
@@ -9659,19 +9666,19 @@
       </c>
     </row>
     <row r="5" ht="28.8" spans="1:5">
-      <c r="A5" s="9">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>310</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>-1</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>302</v>
       </c>
     </row>
@@ -9728,7 +9735,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>312</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -9757,7 +9764,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>312</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -9786,7 +9793,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>312</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -9815,7 +9822,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>312</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -9844,7 +9851,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>312</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -9873,7 +9880,7 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>312</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -9902,7 +9909,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -9920,7 +9927,7 @@
       <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <v>168</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -9931,7 +9938,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -9949,7 +9956,7 @@
       <c r="G9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <v>135</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -9960,7 +9967,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -9978,7 +9985,7 @@
       <c r="G10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="5">
         <v>145</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -9989,7 +9996,7 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -10007,7 +10014,7 @@
       <c r="G11" s="3">
         <v>1</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <v>148</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -10018,7 +10025,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -10036,7 +10043,7 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <v>168</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -10047,7 +10054,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -10065,7 +10072,7 @@
       <c r="G13" s="3">
         <v>1</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="5">
         <v>180</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -10076,7 +10083,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>180</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -10272,10 +10279,10 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D2" s="1">
@@ -10298,10 +10305,10 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D3" s="1">
@@ -10324,10 +10331,10 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D4" s="1">
@@ -10350,10 +10357,10 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D5" s="1">
@@ -10376,10 +10383,10 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D6" s="1">
@@ -10402,10 +10409,10 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D7" s="1">
@@ -10428,10 +10435,10 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D8" s="1">
@@ -10454,10 +10461,10 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D9" s="1">
@@ -10480,10 +10487,10 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D10" s="1">
@@ -10506,10 +10513,10 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D11" s="1">
@@ -10532,10 +10539,10 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D12" s="1">
@@ -10558,10 +10565,10 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D13" s="1">
@@ -10584,10 +10591,10 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D14" s="1">
@@ -10611,7 +10618,7 @@
       <c r="B15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D15" s="1">
@@ -10635,7 +10642,7 @@
       <c r="B16" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D16" s="1">
@@ -10659,7 +10666,7 @@
       <c r="B17" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D17" s="1">
@@ -10683,7 +10690,7 @@
       <c r="B18" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D18" s="1">
@@ -10707,7 +10714,7 @@
       <c r="B19" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>317</v>
       </c>
       <c r="D19" s="1">
@@ -10777,7 +10784,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>320</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -10806,7 +10813,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>320</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -10835,7 +10842,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>320</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -10864,7 +10871,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>320</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -10893,7 +10900,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>320</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -10922,7 +10929,7 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>320</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -10951,7 +10958,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>322</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -10960,7 +10967,7 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>-45</v>
       </c>
       <c r="F8" s="3">
@@ -10969,7 +10976,7 @@
       <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <v>-45</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -10980,7 +10987,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>322</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -10989,7 +10996,7 @@
       <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>-45</v>
       </c>
       <c r="F9" s="3">
@@ -10998,7 +11005,7 @@
       <c r="G9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <v>-45</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -11009,7 +11016,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>322</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -11018,7 +11025,7 @@
       <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>-45</v>
       </c>
       <c r="F10" s="3">
@@ -11027,7 +11034,7 @@
       <c r="G10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="5">
         <v>-45</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -11038,7 +11045,7 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>322</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -11047,7 +11054,7 @@
       <c r="D11" s="1">
         <v>4</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>-45</v>
       </c>
       <c r="F11" s="3">
@@ -11056,7 +11063,7 @@
       <c r="G11" s="3">
         <v>1</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <v>-45</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -11067,7 +11074,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>322</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -11076,7 +11083,7 @@
       <c r="D12" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>-45</v>
       </c>
       <c r="F12" s="3">
@@ -11085,7 +11092,7 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <v>-45</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -11096,7 +11103,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>322</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -11105,7 +11112,7 @@
       <c r="D13" s="1">
         <v>6</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>-45</v>
       </c>
       <c r="F13" s="3">
@@ -11114,7 +11121,7 @@
       <c r="G13" s="3">
         <v>1</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="5">
         <v>-45</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -11125,7 +11132,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>180</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -11554,7 +11561,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -11583,7 +11590,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -11612,7 +11619,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -11641,7 +11648,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -11670,7 +11677,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -11699,7 +11706,7 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -11728,7 +11735,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>326</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -11737,7 +11744,7 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>-30</v>
       </c>
       <c r="F8" s="3">
@@ -11746,7 +11753,7 @@
       <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <v>-30</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -11757,7 +11764,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>326</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -11766,7 +11773,7 @@
       <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <v>-30</v>
       </c>
       <c r="F9" s="3">
@@ -11775,7 +11782,7 @@
       <c r="G9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <v>-30</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -11786,7 +11793,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>326</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -11795,7 +11802,7 @@
       <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <v>-30</v>
       </c>
       <c r="F10" s="3">
@@ -11804,7 +11811,7 @@
       <c r="G10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="5">
         <v>-30</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -11815,7 +11822,7 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>326</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -11824,7 +11831,7 @@
       <c r="D11" s="1">
         <v>4</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>-30</v>
       </c>
       <c r="F11" s="3">
@@ -11833,7 +11840,7 @@
       <c r="G11" s="3">
         <v>1</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="5">
         <v>-30</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -11844,7 +11851,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>326</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -11853,7 +11860,7 @@
       <c r="D12" s="1">
         <v>5</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <v>-30</v>
       </c>
       <c r="F12" s="3">
@@ -11862,7 +11869,7 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <v>-30</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -11873,7 +11880,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>326</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -11882,7 +11889,7 @@
       <c r="D13" s="1">
         <v>6</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <v>-30</v>
       </c>
       <c r="F13" s="3">
@@ -11891,7 +11898,7 @@
       <c r="G13" s="3">
         <v>1</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="5">
         <v>-30</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -11902,7 +11909,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>180</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -12011,7 +12018,7 @@
       <c r="D18" s="1">
         <v>1</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <v>351</v>
       </c>
       <c r="F18" s="3">
@@ -12036,7 +12043,7 @@
       <c r="D19" s="1">
         <v>1</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>-351</v>
       </c>
       <c r="F19" s="3">
@@ -12061,7 +12068,7 @@
       <c r="D20" s="1">
         <v>2</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <v>351</v>
       </c>
       <c r="F20" s="3">
@@ -12086,7 +12093,7 @@
       <c r="D21" s="1">
         <v>2</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <v>-351</v>
       </c>
       <c r="F21" s="3">
@@ -12111,7 +12118,7 @@
       <c r="D22" s="1">
         <v>3</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <v>525</v>
       </c>
       <c r="F22" s="3">
@@ -12136,7 +12143,7 @@
       <c r="D23" s="1">
         <v>3</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <v>-42</v>
       </c>
       <c r="F23" s="3">
@@ -12161,7 +12168,7 @@
       <c r="D24" s="1">
         <v>4</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <v>181</v>
       </c>
       <c r="F24" s="3">
@@ -12186,7 +12193,7 @@
       <c r="D25" s="1">
         <v>4</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <v>-181</v>
       </c>
       <c r="F25" s="3">
@@ -12211,7 +12218,7 @@
       <c r="D26" s="1">
         <v>5</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <v>181</v>
       </c>
       <c r="F26" s="3">
@@ -12236,7 +12243,7 @@
       <c r="D27" s="1">
         <v>5</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <v>-181</v>
       </c>
       <c r="F27" s="3">
@@ -12261,7 +12268,7 @@
       <c r="D28" s="1">
         <v>6</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <v>181</v>
       </c>
       <c r="F28" s="3">
@@ -12286,7 +12293,7 @@
       <c r="D29" s="1">
         <v>6</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <v>-181</v>
       </c>
       <c r="F29" s="3">
@@ -13576,7 +13583,7 @@
       <c r="C20" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>356</v>
       </c>
       <c r="E20" s="3">
@@ -13596,7 +13603,7 @@
       <c r="C21" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>357</v>
       </c>
       <c r="E21" s="3">
@@ -13616,7 +13623,7 @@
       <c r="C22" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>126</v>
       </c>
       <c r="E22" s="3">
@@ -13636,7 +13643,7 @@
       <c r="C23" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>126</v>
       </c>
       <c r="E23" s="3">
@@ -13850,7 +13857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="57.6" spans="1:8">
+    <row r="8" s="1" customFormat="1" ht="28.8" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -14667,6 +14674,358 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.2222222222222" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1111111111111" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="5" width="9" style="3"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="28.8" spans="1:7">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="28.8" spans="1:7">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="28.8" spans="1:7">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" spans="1:7">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:7">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:7">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="28.8" spans="1:7">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:7">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D13" s="3">
+        <v>6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" ht="28.8" spans="1:7">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" ht="28.8" spans="1:7">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D15" s="3">
+        <v>7</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
